--- a/artfynd/A 53589-2025 artfynd.xlsx
+++ b/artfynd/A 53589-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129953592</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129953590</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129953585</v>
       </c>
       <c r="B4" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129953591</v>
       </c>
       <c r="B5" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 53589-2025 artfynd.xlsx
+++ b/artfynd/A 53589-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129953585</v>
       </c>
       <c r="B4" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53589-2025 artfynd.xlsx
+++ b/artfynd/A 53589-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129953585</v>
       </c>
       <c r="B4" t="n">
-        <v>97044</v>
+        <v>97061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53589-2025 artfynd.xlsx
+++ b/artfynd/A 53589-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129953585</v>
       </c>
       <c r="B4" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53589-2025 artfynd.xlsx
+++ b/artfynd/A 53589-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129953592</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129953590</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129953585</v>
       </c>
       <c r="B4" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129953591</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 53589-2025 artfynd.xlsx
+++ b/artfynd/A 53589-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129953592</v>
+        <v>129953590</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636520</v>
+        <v>636348</v>
       </c>
       <c r="R2" t="n">
-        <v>6644575</v>
+        <v>6644654</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129953590</v>
+        <v>129953591</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636348</v>
+        <v>636412</v>
       </c>
       <c r="R3" t="n">
-        <v>6644654</v>
+        <v>6644538</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129953585</v>
+        <v>129953592</v>
       </c>
       <c r="B4" t="n">
-        <v>97166</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636545</v>
+        <v>636520</v>
       </c>
       <c r="R4" t="n">
-        <v>6644456</v>
+        <v>6644575</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129953591</v>
+        <v>129953585</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636412</v>
+        <v>636545</v>
       </c>
       <c r="R5" t="n">
-        <v>6644538</v>
+        <v>6644456</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
